--- a/data/zhou/data_zhou_cleaned.xlsx
+++ b/data/zhou/data_zhou_cleaned.xlsx
@@ -5237,12 +5237,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>defect_size_m</t>
+          <t>sqrt_A_um</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>defect_position_m</t>
+          <t>defect_position_um</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>defect_size_m</t>
+          <t>sqrt_A_um</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>defect_position_m</t>
+          <t>defect_position_um</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>sqrt_A</t>
+          <t>sqrt_A_um</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
